--- a/descriptive tables/desc_totalincome.xlsx
+++ b/descriptive tables/desc_totalincome.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
-    <t xml:space="preserve">variable</t>
+    <t xml:space="preserve">province</t>
   </si>
   <si>
-    <t xml:space="preserve">province</t>
+    <t xml:space="preserve">variable</t>
   </si>
   <si>
     <t xml:space="preserve">mean_value</t>
@@ -312,11 +312,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.58"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -325,163 +322,197 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>766568.385714286</v>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>582306.331753555</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>220506.208115595</v>
+      <c r="B3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>175562.989576423</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>951797.601226994</v>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>572080.53722334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>202102.844251755</v>
+      <c r="B5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>151891.165391608</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>896301.578703704</v>
+      <c r="A6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>714180.880642693</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>252378.428984621</v>
+      <c r="A7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>219540.108065379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>947949.949541284</v>
+      <c r="A8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>752740.671081678</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>304206.910273773</v>
+      <c r="A9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>229934.641592207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="0" t="n">
+      <c r="A10" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>1000625.68508287</v>
+      <c r="B10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>676748.39703154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="0" t="n">
+      <c r="A11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>272555.770535166</v>
+      <c r="B11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>185629.259365521</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="0" t="n">
+      <c r="A12" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>778713.274193548</v>
-      </c>
+      <c r="B12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>627315.077562327</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="0" t="n">
+      <c r="A13" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>218166.484706221</v>
-      </c>
+      <c r="B13" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>182023.217655982</v>
+      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="0" t="n">
+      <c r="A14" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>501866.70357377</v>
-      </c>
+      <c r="B14" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>459883.334987593</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="0" t="n">
+      <c r="A15" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>134950.713370804</v>
-      </c>
+      <c r="B15" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>133440.98965103</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
